--- a/Team-Data/2008-09/1-25-2008-09.xlsx
+++ b/Team-Data/2008-09/1-25-2008-09.xlsx
@@ -50,7 +50,6 @@
       <right style="thin"/>
       <top style="thin"/>
       <bottom style="thin"/>
-      <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="1">
@@ -66,6 +65,74 @@
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
+  <colors>
+    <indexedColors>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00000000"/>
+      <rgbColor rgb="00FFFFFF"/>
+      <rgbColor rgb="00FF0000"/>
+      <rgbColor rgb="0000FF00"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008000"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00808000"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="00C0C0C0"/>
+      <rgbColor rgb="00808080"/>
+      <rgbColor rgb="009999FF"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00FFFFCC"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00660066"/>
+      <rgbColor rgb="00FF8080"/>
+      <rgbColor rgb="000066CC"/>
+      <rgbColor rgb="00CCCCFF"/>
+      <rgbColor rgb="00000080"/>
+      <rgbColor rgb="00FF00FF"/>
+      <rgbColor rgb="00FFFF00"/>
+      <rgbColor rgb="0000FFFF"/>
+      <rgbColor rgb="00800080"/>
+      <rgbColor rgb="00800000"/>
+      <rgbColor rgb="00008080"/>
+      <rgbColor rgb="000000FF"/>
+      <rgbColor rgb="0000CCFF"/>
+      <rgbColor rgb="00CCFFFF"/>
+      <rgbColor rgb="00CCFFCC"/>
+      <rgbColor rgb="00FFFF99"/>
+      <rgbColor rgb="0099CCFF"/>
+      <rgbColor rgb="00FF99CC"/>
+      <rgbColor rgb="00CC99FF"/>
+      <rgbColor rgb="00FFCC99"/>
+      <rgbColor rgb="003366FF"/>
+      <rgbColor rgb="0033CCCC"/>
+      <rgbColor rgb="0099CC00"/>
+      <rgbColor rgb="00FFCC00"/>
+      <rgbColor rgb="00FF9900"/>
+      <rgbColor rgb="00FF6600"/>
+      <rgbColor rgb="00666699"/>
+      <rgbColor rgb="00969696"/>
+      <rgbColor rgb="00003366"/>
+      <rgbColor rgb="00339966"/>
+      <rgbColor rgb="00003300"/>
+      <rgbColor rgb="00333300"/>
+      <rgbColor rgb="00993300"/>
+      <rgbColor rgb="00993366"/>
+      <rgbColor rgb="00333399"/>
+      <rgbColor rgb="00333333"/>
+    </indexedColors>
+  </colors>
 </styleSheet>
 </file>
 
@@ -661,16 +728,16 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E2" t="n">
         <v>26</v>
       </c>
       <c r="F2" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="G2" t="n">
-        <v>0.605</v>
+        <v>0.619</v>
       </c>
       <c r="H2" t="n">
         <v>48.1</v>
@@ -679,31 +746,31 @@
         <v>36.1</v>
       </c>
       <c r="J2" t="n">
-        <v>79</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K2" t="n">
-        <v>0.457</v>
+        <v>0.458</v>
       </c>
       <c r="L2" t="n">
-        <v>8</v>
+        <v>8.1</v>
       </c>
       <c r="M2" t="n">
         <v>21.5</v>
       </c>
       <c r="N2" t="n">
-        <v>0.372</v>
+        <v>0.376</v>
       </c>
       <c r="O2" t="n">
-        <v>18.5</v>
+        <v>18.4</v>
       </c>
       <c r="P2" t="n">
-        <v>24.9</v>
+        <v>24.8</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.744</v>
+        <v>0.742</v>
       </c>
       <c r="R2" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="S2" t="n">
         <v>29.7</v>
@@ -718,7 +785,7 @@
         <v>13</v>
       </c>
       <c r="W2" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="X2" t="n">
         <v>4.7</v>
@@ -727,40 +794,40 @@
         <v>4.4</v>
       </c>
       <c r="Z2" t="n">
-        <v>20.2</v>
+        <v>19.9</v>
       </c>
       <c r="AA2" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="AB2" t="n">
         <v>98.7</v>
       </c>
       <c r="AC2" t="n">
-        <v>2.1</v>
+        <v>2.3</v>
       </c>
       <c r="AD2" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AE2" t="n">
         <v>8</v>
       </c>
       <c r="AF2" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AG2" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AH2" t="n">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="AI2" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AJ2" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AK2" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AL2" t="n">
         <v>4</v>
@@ -769,16 +836,16 @@
         <v>3</v>
       </c>
       <c r="AN2" t="n">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="AO2" t="n">
-        <v>20</v>
+        <v>22</v>
       </c>
       <c r="AP2" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AQ2" t="n">
-        <v>26</v>
+        <v>28</v>
       </c>
       <c r="AR2" t="n">
         <v>20</v>
@@ -793,10 +860,10 @@
         <v>8</v>
       </c>
       <c r="AV2" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AW2" t="n">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="AX2" t="n">
         <v>18</v>
@@ -805,10 +872,10 @@
         <v>11</v>
       </c>
       <c r="AZ2" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="BA2" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BB2" t="n">
         <v>14</v>
@@ -826,7 +893,7 @@
       </c>
       <c r="BF2" t="inlineStr">
         <is>
-          <t>1-25-2008-09</t>
+          <t>2009-01-25</t>
         </is>
       </c>
     </row>
@@ -858,34 +925,34 @@
         <v>48.4</v>
       </c>
       <c r="I3" t="n">
-        <v>37.2</v>
+        <v>36.8</v>
       </c>
       <c r="J3" t="n">
-        <v>77</v>
+        <v>76.59999999999999</v>
       </c>
       <c r="K3" t="n">
-        <v>0.482</v>
+        <v>0.48</v>
       </c>
       <c r="L3" t="n">
-        <v>6.7</v>
+        <v>6.4</v>
       </c>
       <c r="M3" t="n">
-        <v>17.3</v>
+        <v>17</v>
       </c>
       <c r="N3" t="n">
-        <v>0.388</v>
+        <v>0.378</v>
       </c>
       <c r="O3" t="n">
-        <v>20.3</v>
+        <v>20.6</v>
       </c>
       <c r="P3" t="n">
-        <v>26.3</v>
+        <v>26.8</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.773</v>
+        <v>0.769</v>
       </c>
       <c r="R3" t="n">
-        <v>10.8</v>
+        <v>10.9</v>
       </c>
       <c r="S3" t="n">
         <v>32</v>
@@ -894,34 +961,34 @@
         <v>42.8</v>
       </c>
       <c r="U3" t="n">
-        <v>22.5</v>
+        <v>22.1</v>
       </c>
       <c r="V3" t="n">
-        <v>15.9</v>
+        <v>16.1</v>
       </c>
       <c r="W3" t="n">
         <v>8.5</v>
       </c>
       <c r="X3" t="n">
-        <v>4.9</v>
+        <v>4.8</v>
       </c>
       <c r="Y3" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="Z3" t="n">
         <v>23.1</v>
       </c>
       <c r="AA3" t="n">
-        <v>22.8</v>
+        <v>23.1</v>
       </c>
       <c r="AB3" t="n">
-        <v>101.4</v>
+        <v>100.6</v>
       </c>
       <c r="AC3" t="n">
-        <v>10</v>
+        <v>9.6</v>
       </c>
       <c r="AD3" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AE3" t="n">
         <v>1</v>
@@ -933,34 +1000,34 @@
         <v>3</v>
       </c>
       <c r="AH3" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AI3" t="n">
-        <v>10</v>
+        <v>14</v>
       </c>
       <c r="AJ3" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="AK3" t="n">
         <v>2</v>
       </c>
       <c r="AL3" t="n">
-        <v>15</v>
+        <v>17</v>
       </c>
       <c r="AM3" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AN3" t="n">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c r="AO3" t="n">
+        <v>5</v>
+      </c>
+      <c r="AP3" t="n">
         <v>6</v>
       </c>
-      <c r="AP3" t="n">
-        <v>7</v>
-      </c>
       <c r="AQ3" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AR3" t="n">
         <v>16</v>
@@ -993,7 +1060,7 @@
         <v>4</v>
       </c>
       <c r="BB3" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BC3" t="n">
         <v>2</v>
@@ -1008,7 +1075,7 @@
       </c>
       <c r="BF3" t="inlineStr">
         <is>
-          <t>1-25-2008-09</t>
+          <t>2009-01-25</t>
         </is>
       </c>
     </row>
@@ -1025,16 +1092,16 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E4" t="n">
         <v>18</v>
       </c>
       <c r="F4" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="G4" t="n">
-        <v>0.409</v>
+        <v>0.419</v>
       </c>
       <c r="H4" t="n">
         <v>48.6</v>
@@ -1043,31 +1110,31 @@
         <v>33.9</v>
       </c>
       <c r="J4" t="n">
-        <v>75.90000000000001</v>
+        <v>75.8</v>
       </c>
       <c r="K4" t="n">
-        <v>0.446</v>
+        <v>0.447</v>
       </c>
       <c r="L4" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="M4" t="n">
-        <v>15.2</v>
+        <v>15</v>
       </c>
       <c r="N4" t="n">
-        <v>0.354</v>
+        <v>0.356</v>
       </c>
       <c r="O4" t="n">
         <v>18.5</v>
       </c>
       <c r="P4" t="n">
-        <v>24.8</v>
+        <v>24.7</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.746</v>
+        <v>0.75</v>
       </c>
       <c r="R4" t="n">
-        <v>10.6</v>
+        <v>10.7</v>
       </c>
       <c r="S4" t="n">
         <v>28.7</v>
@@ -1076,25 +1143,25 @@
         <v>39.3</v>
       </c>
       <c r="U4" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="V4" t="n">
-        <v>15.4</v>
+        <v>15.5</v>
       </c>
       <c r="W4" t="n">
-        <v>7.2</v>
+        <v>7.1</v>
       </c>
       <c r="X4" t="n">
         <v>4.6</v>
       </c>
       <c r="Y4" t="n">
-        <v>6</v>
+        <v>5.9</v>
       </c>
       <c r="Z4" t="n">
-        <v>22.1</v>
+        <v>22.2</v>
       </c>
       <c r="AA4" t="n">
-        <v>21.1</v>
+        <v>21.2</v>
       </c>
       <c r="AB4" t="n">
         <v>91.59999999999999</v>
@@ -1103,19 +1170,19 @@
         <v>-1.7</v>
       </c>
       <c r="AD4" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AE4" t="n">
         <v>19</v>
       </c>
       <c r="AF4" t="n">
-        <v>20</v>
+        <v>18</v>
       </c>
       <c r="AG4" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AH4" t="n">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="AI4" t="n">
         <v>30</v>
@@ -1124,7 +1191,7 @@
         <v>30</v>
       </c>
       <c r="AK4" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AL4" t="n">
         <v>23</v>
@@ -1136,7 +1203,7 @@
         <v>20</v>
       </c>
       <c r="AO4" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AP4" t="n">
         <v>18</v>
@@ -1151,16 +1218,16 @@
         <v>27</v>
       </c>
       <c r="AT4" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AU4" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AV4" t="n">
         <v>25</v>
       </c>
       <c r="AW4" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AX4" t="n">
         <v>19</v>
@@ -1169,7 +1236,7 @@
         <v>29</v>
       </c>
       <c r="AZ4" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="BA4" t="n">
         <v>13</v>
@@ -1190,7 +1257,7 @@
       </c>
       <c r="BF4" t="inlineStr">
         <is>
-          <t>1-25-2008-09</t>
+          <t>2009-01-25</t>
         </is>
       </c>
     </row>
@@ -1210,64 +1277,64 @@
         <v>44</v>
       </c>
       <c r="E5" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="F5" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="G5" t="n">
-        <v>0.386</v>
+        <v>0.409</v>
       </c>
       <c r="H5" t="n">
-        <v>48.7</v>
+        <v>48.6</v>
       </c>
       <c r="I5" t="n">
-        <v>37.3</v>
+        <v>37.1</v>
       </c>
       <c r="J5" t="n">
-        <v>84.09999999999999</v>
+        <v>83.7</v>
       </c>
       <c r="K5" t="n">
-        <v>0.443</v>
+        <v>0.444</v>
       </c>
       <c r="L5" t="n">
         <v>6.2</v>
       </c>
       <c r="M5" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="N5" t="n">
-        <v>0.374</v>
+        <v>0.375</v>
       </c>
       <c r="O5" t="n">
-        <v>18.4</v>
+        <v>18.7</v>
       </c>
       <c r="P5" t="n">
-        <v>23.1</v>
+        <v>23.5</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.794</v>
+        <v>0.793</v>
       </c>
       <c r="R5" t="n">
         <v>11.9</v>
       </c>
       <c r="S5" t="n">
-        <v>30.4</v>
+        <v>30.3</v>
       </c>
       <c r="T5" t="n">
         <v>42.2</v>
       </c>
       <c r="U5" t="n">
-        <v>20.6</v>
+        <v>20.7</v>
       </c>
       <c r="V5" t="n">
-        <v>15.1</v>
+        <v>15.2</v>
       </c>
       <c r="W5" t="n">
         <v>7.3</v>
       </c>
       <c r="X5" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Y5" t="n">
         <v>5.5</v>
@@ -1276,58 +1343,58 @@
         <v>22.2</v>
       </c>
       <c r="AA5" t="n">
-        <v>20.1</v>
+        <v>20.3</v>
       </c>
       <c r="AB5" t="n">
         <v>99.09999999999999</v>
       </c>
       <c r="AC5" t="n">
-        <v>-3.8</v>
+        <v>-3.5</v>
       </c>
       <c r="AD5" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AE5" t="n">
-        <v>22</v>
+        <v>19</v>
       </c>
       <c r="AF5" t="n">
         <v>21</v>
       </c>
       <c r="AG5" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AH5" t="n">
-        <v>3</v>
+        <v>8</v>
       </c>
       <c r="AI5" t="n">
         <v>9</v>
       </c>
       <c r="AJ5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AK5" t="n">
         <v>26</v>
       </c>
       <c r="AL5" t="n">
+        <v>19</v>
+      </c>
+      <c r="AM5" t="n">
+        <v>21</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>13</v>
+      </c>
+      <c r="AO5" t="n">
+        <v>19</v>
+      </c>
+      <c r="AP5" t="n">
         <v>20</v>
-      </c>
-      <c r="AM5" t="n">
-        <v>20</v>
-      </c>
-      <c r="AN5" t="n">
-        <v>12</v>
-      </c>
-      <c r="AO5" t="n">
-        <v>22</v>
-      </c>
-      <c r="AP5" t="n">
-        <v>23</v>
       </c>
       <c r="AQ5" t="n">
         <v>8</v>
       </c>
       <c r="AR5" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AS5" t="n">
         <v>13</v>
@@ -1336,25 +1403,25 @@
         <v>11</v>
       </c>
       <c r="AU5" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AV5" t="n">
-        <v>21</v>
+        <v>23</v>
       </c>
       <c r="AW5" t="n">
         <v>13</v>
       </c>
       <c r="AX5" t="n">
-        <v>4</v>
+        <v>6</v>
       </c>
       <c r="AY5" t="n">
+        <v>24</v>
+      </c>
+      <c r="AZ5" t="n">
+        <v>22</v>
+      </c>
+      <c r="BA5" t="n">
         <v>23</v>
-      </c>
-      <c r="AZ5" t="n">
-        <v>23</v>
-      </c>
-      <c r="BA5" t="n">
-        <v>24</v>
       </c>
       <c r="BB5" t="n">
         <v>12</v>
@@ -1372,7 +1439,7 @@
       </c>
       <c r="BF5" t="inlineStr">
         <is>
-          <t>1-25-2008-09</t>
+          <t>2009-01-25</t>
         </is>
       </c>
     </row>
@@ -1389,85 +1456,85 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>41</v>
+        <v>42</v>
       </c>
       <c r="E6" t="n">
         <v>34</v>
       </c>
       <c r="F6" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="G6" t="n">
-        <v>0.829</v>
+        <v>0.8100000000000001</v>
       </c>
       <c r="H6" t="n">
         <v>48.1</v>
       </c>
       <c r="I6" t="n">
-        <v>37.4</v>
+        <v>37.2</v>
       </c>
       <c r="J6" t="n">
-        <v>78.3</v>
+        <v>78</v>
       </c>
       <c r="K6" t="n">
-        <v>0.478</v>
+        <v>0.477</v>
       </c>
       <c r="L6" t="n">
-        <v>7.7</v>
+        <v>7.6</v>
       </c>
       <c r="M6" t="n">
-        <v>20.8</v>
+        <v>20.6</v>
       </c>
       <c r="N6" t="n">
-        <v>0.371</v>
+        <v>0.368</v>
       </c>
       <c r="O6" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="P6" t="n">
-        <v>24.9</v>
+        <v>25</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.752</v>
+        <v>0.751</v>
       </c>
       <c r="R6" t="n">
-        <v>10.6</v>
+        <v>10.5</v>
       </c>
       <c r="S6" t="n">
-        <v>31</v>
+        <v>31.1</v>
       </c>
       <c r="T6" t="n">
         <v>41.6</v>
       </c>
       <c r="U6" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="V6" t="n">
-        <v>13</v>
+        <v>13.2</v>
       </c>
       <c r="W6" t="n">
         <v>7.9</v>
       </c>
       <c r="X6" t="n">
-        <v>5.9</v>
+        <v>5.8</v>
       </c>
       <c r="Y6" t="n">
-        <v>4</v>
+        <v>3.9</v>
       </c>
       <c r="Z6" t="n">
-        <v>20.7</v>
+        <v>20.8</v>
       </c>
       <c r="AA6" t="n">
-        <v>20.9</v>
+        <v>21</v>
       </c>
       <c r="AB6" t="n">
-        <v>101.2</v>
+        <v>100.8</v>
       </c>
       <c r="AC6" t="n">
-        <v>11.1</v>
+        <v>10.7</v>
       </c>
       <c r="AD6" t="n">
-        <v>29</v>
+        <v>20</v>
       </c>
       <c r="AE6" t="n">
         <v>2</v>
@@ -1485,13 +1552,13 @@
         <v>8</v>
       </c>
       <c r="AJ6" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="AK6" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AL6" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AM6" t="n">
         <v>4</v>
@@ -1503,10 +1570,10 @@
         <v>18</v>
       </c>
       <c r="AP6" t="n">
-        <v>17</v>
+        <v>12</v>
       </c>
       <c r="AQ6" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AR6" t="n">
         <v>19</v>
@@ -1515,31 +1582,31 @@
         <v>10</v>
       </c>
       <c r="AT6" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AU6" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AV6" t="n">
+        <v>7</v>
+      </c>
+      <c r="AW6" t="n">
         <v>6</v>
-      </c>
-      <c r="AW6" t="n">
-        <v>7</v>
       </c>
       <c r="AX6" t="n">
         <v>3</v>
       </c>
       <c r="AY6" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AZ6" t="n">
-        <v>12</v>
+        <v>15</v>
       </c>
       <c r="BA6" t="n">
-        <v>18</v>
+        <v>15</v>
       </c>
       <c r="BB6" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BC6" t="n">
         <v>1</v>
@@ -1554,7 +1621,7 @@
       </c>
       <c r="BF6" t="inlineStr">
         <is>
-          <t>1-25-2008-09</t>
+          <t>2009-01-25</t>
         </is>
       </c>
     </row>
@@ -1571,28 +1638,28 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E7" t="n">
         <v>25</v>
       </c>
       <c r="F7" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G7" t="n">
-        <v>0.5679999999999999</v>
+        <v>0.581</v>
       </c>
       <c r="H7" t="n">
         <v>48.3</v>
       </c>
       <c r="I7" t="n">
-        <v>37.6</v>
+        <v>37.7</v>
       </c>
       <c r="J7" t="n">
-        <v>83.09999999999999</v>
+        <v>83.2</v>
       </c>
       <c r="K7" t="n">
-        <v>0.452</v>
+        <v>0.453</v>
       </c>
       <c r="L7" t="n">
         <v>6.9</v>
@@ -1601,34 +1668,34 @@
         <v>20.5</v>
       </c>
       <c r="N7" t="n">
-        <v>0.337</v>
+        <v>0.338</v>
       </c>
       <c r="O7" t="n">
-        <v>17.8</v>
+        <v>17.5</v>
       </c>
       <c r="P7" t="n">
-        <v>21.8</v>
+        <v>21.5</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.8159999999999999</v>
+        <v>0.8149999999999999</v>
       </c>
       <c r="R7" t="n">
         <v>11.6</v>
       </c>
       <c r="S7" t="n">
-        <v>31.8</v>
+        <v>31.9</v>
       </c>
       <c r="T7" t="n">
-        <v>43.4</v>
+        <v>43.5</v>
       </c>
       <c r="U7" t="n">
-        <v>21.2</v>
+        <v>21.4</v>
       </c>
       <c r="V7" t="n">
-        <v>13.3</v>
+        <v>13.2</v>
       </c>
       <c r="W7" t="n">
-        <v>7</v>
+        <v>7.1</v>
       </c>
       <c r="X7" t="n">
         <v>5.4</v>
@@ -1637,28 +1704,28 @@
         <v>4.3</v>
       </c>
       <c r="Z7" t="n">
-        <v>18.7</v>
+        <v>18.8</v>
       </c>
       <c r="AA7" t="n">
-        <v>19.6</v>
+        <v>19.4</v>
       </c>
       <c r="AB7" t="n">
         <v>99.90000000000001</v>
       </c>
       <c r="AC7" t="n">
-        <v>0.5</v>
+        <v>1</v>
       </c>
       <c r="AD7" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AE7" t="n">
         <v>11</v>
       </c>
       <c r="AF7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AG7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AH7" t="n">
         <v>16</v>
@@ -1670,7 +1737,7 @@
         <v>7</v>
       </c>
       <c r="AK7" t="n">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="AL7" t="n">
         <v>12</v>
@@ -1700,22 +1767,22 @@
         <v>3</v>
       </c>
       <c r="AU7" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AV7" t="n">
         <v>8</v>
       </c>
       <c r="AW7" t="n">
-        <v>19</v>
+        <v>16</v>
       </c>
       <c r="AX7" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AY7" t="n">
         <v>8</v>
       </c>
       <c r="AZ7" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="BA7" t="n">
         <v>27</v>
@@ -1724,7 +1791,7 @@
         <v>11</v>
       </c>
       <c r="BC7" t="n">
-        <v>15</v>
+        <v>12</v>
       </c>
       <c r="BD7" t="n">
         <v>10</v>
@@ -1736,7 +1803,7 @@
       </c>
       <c r="BF7" t="inlineStr">
         <is>
-          <t>1-25-2008-09</t>
+          <t>2009-01-25</t>
         </is>
       </c>
     </row>
@@ -1753,88 +1820,88 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E8" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="F8" t="n">
         <v>15</v>
       </c>
       <c r="G8" t="n">
-        <v>0.659</v>
+        <v>0.651</v>
       </c>
       <c r="H8" t="n">
         <v>48.2</v>
       </c>
       <c r="I8" t="n">
-        <v>37.1</v>
+        <v>37</v>
       </c>
       <c r="J8" t="n">
-        <v>78.59999999999999</v>
+        <v>78.3</v>
       </c>
       <c r="K8" t="n">
         <v>0.472</v>
       </c>
       <c r="L8" t="n">
-        <v>6.8</v>
+        <v>6.7</v>
       </c>
       <c r="M8" t="n">
-        <v>18</v>
+        <v>17.9</v>
       </c>
       <c r="N8" t="n">
-        <v>0.375</v>
+        <v>0.376</v>
       </c>
       <c r="O8" t="n">
         <v>23.7</v>
       </c>
       <c r="P8" t="n">
-        <v>31.4</v>
+        <v>31.3</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.755</v>
+        <v>0.757</v>
       </c>
       <c r="R8" t="n">
-        <v>10.5</v>
+        <v>10.3</v>
       </c>
       <c r="S8" t="n">
         <v>30.7</v>
       </c>
       <c r="T8" t="n">
-        <v>41.2</v>
+        <v>41</v>
       </c>
       <c r="U8" t="n">
-        <v>23</v>
+        <v>22.9</v>
       </c>
       <c r="V8" t="n">
-        <v>15.5</v>
+        <v>15.6</v>
       </c>
       <c r="W8" t="n">
-        <v>9</v>
+        <v>8.9</v>
       </c>
       <c r="X8" t="n">
-        <v>5.7</v>
+        <v>5.6</v>
       </c>
       <c r="Y8" t="n">
         <v>5.6</v>
       </c>
       <c r="Z8" t="n">
-        <v>22.4</v>
+        <v>22.2</v>
       </c>
       <c r="AA8" t="n">
         <v>23.6</v>
       </c>
       <c r="AB8" t="n">
-        <v>104.6</v>
+        <v>104.3</v>
       </c>
       <c r="AC8" t="n">
-        <v>3.8</v>
+        <v>3.4</v>
       </c>
       <c r="AD8" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AE8" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AF8" t="n">
         <v>7</v>
@@ -1849,7 +1916,7 @@
         <v>11</v>
       </c>
       <c r="AJ8" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AK8" t="n">
         <v>6</v>
@@ -1861,7 +1928,7 @@
         <v>15</v>
       </c>
       <c r="AN8" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AO8" t="n">
         <v>1</v>
@@ -1870,19 +1937,19 @@
         <v>1</v>
       </c>
       <c r="AQ8" t="n">
-        <v>21</v>
+        <v>19</v>
       </c>
       <c r="AR8" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AS8" t="n">
         <v>12</v>
       </c>
       <c r="AT8" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AU8" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AV8" t="n">
         <v>26</v>
@@ -1891,10 +1958,10 @@
         <v>1</v>
       </c>
       <c r="AX8" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AY8" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AZ8" t="n">
         <v>24</v>
@@ -1918,7 +1985,7 @@
       </c>
       <c r="BF8" t="inlineStr">
         <is>
-          <t>1-25-2008-09</t>
+          <t>2009-01-25</t>
         </is>
       </c>
     </row>
@@ -1935,106 +2002,106 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E9" t="n">
         <v>24</v>
       </c>
       <c r="F9" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5580000000000001</v>
+        <v>0.571</v>
       </c>
       <c r="H9" t="n">
-        <v>48.3</v>
+        <v>48.4</v>
       </c>
       <c r="I9" t="n">
-        <v>36</v>
+        <v>35.8</v>
       </c>
       <c r="J9" t="n">
         <v>79</v>
       </c>
       <c r="K9" t="n">
-        <v>0.455</v>
+        <v>0.453</v>
       </c>
       <c r="L9" t="n">
-        <v>4.7</v>
+        <v>4.6</v>
       </c>
       <c r="M9" t="n">
-        <v>13.7</v>
+        <v>13.8</v>
       </c>
       <c r="N9" t="n">
-        <v>0.34</v>
+        <v>0.337</v>
       </c>
       <c r="O9" t="n">
-        <v>16.8</v>
+        <v>17</v>
       </c>
       <c r="P9" t="n">
         <v>22.7</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.743</v>
+        <v>0.747</v>
       </c>
       <c r="R9" t="n">
         <v>10.7</v>
       </c>
       <c r="S9" t="n">
-        <v>30</v>
+        <v>30.1</v>
       </c>
       <c r="T9" t="n">
-        <v>40.6</v>
+        <v>40.8</v>
       </c>
       <c r="U9" t="n">
-        <v>20.2</v>
+        <v>20</v>
       </c>
       <c r="V9" t="n">
-        <v>12.1</v>
+        <v>12.2</v>
       </c>
       <c r="W9" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="X9" t="n">
         <v>5.1</v>
       </c>
       <c r="Y9" t="n">
-        <v>3.8</v>
+        <v>3.9</v>
       </c>
       <c r="Z9" t="n">
-        <v>21.2</v>
+        <v>21.1</v>
       </c>
       <c r="AA9" t="n">
         <v>20.2</v>
       </c>
       <c r="AB9" t="n">
-        <v>93.5</v>
+        <v>93.2</v>
       </c>
       <c r="AC9" t="n">
         <v>0</v>
       </c>
       <c r="AD9" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AE9" t="n">
         <v>13</v>
       </c>
       <c r="AF9" t="n">
+        <v>11</v>
+      </c>
+      <c r="AG9" t="n">
         <v>12</v>
       </c>
-      <c r="AG9" t="n">
-        <v>13</v>
-      </c>
       <c r="AH9" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AI9" t="n">
         <v>24</v>
       </c>
       <c r="AJ9" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AK9" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AL9" t="n">
         <v>26</v>
@@ -2043,7 +2110,7 @@
         <v>26</v>
       </c>
       <c r="AN9" t="n">
-        <v>24</v>
+        <v>26</v>
       </c>
       <c r="AO9" t="n">
         <v>28</v>
@@ -2052,25 +2119,25 @@
         <v>25</v>
       </c>
       <c r="AQ9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AR9" t="n">
         <v>17</v>
       </c>
       <c r="AS9" t="n">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="AT9" t="n">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="AU9" t="n">
-        <v>22</v>
+        <v>24</v>
       </c>
       <c r="AV9" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AW9" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AX9" t="n">
         <v>11</v>
@@ -2082,10 +2149,10 @@
         <v>17</v>
       </c>
       <c r="BA9" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="BB9" t="n">
-        <v>27</v>
+        <v>28</v>
       </c>
       <c r="BC9" t="n">
         <v>16</v>
@@ -2100,7 +2167,7 @@
       </c>
       <c r="BF9" t="inlineStr">
         <is>
-          <t>1-25-2008-09</t>
+          <t>2009-01-25</t>
         </is>
       </c>
     </row>
@@ -2117,58 +2184,58 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E10" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="F10" t="n">
         <v>31</v>
       </c>
       <c r="G10" t="n">
-        <v>0.311</v>
+        <v>0.295</v>
       </c>
       <c r="H10" t="n">
         <v>48.7</v>
       </c>
       <c r="I10" t="n">
-        <v>39</v>
+        <v>38.9</v>
       </c>
       <c r="J10" t="n">
         <v>86</v>
       </c>
       <c r="K10" t="n">
-        <v>0.453</v>
+        <v>0.452</v>
       </c>
       <c r="L10" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="M10" t="n">
-        <v>18.1</v>
+        <v>18.2</v>
       </c>
       <c r="N10" t="n">
-        <v>0.362</v>
+        <v>0.359</v>
       </c>
       <c r="O10" t="n">
-        <v>22.8</v>
+        <v>23</v>
       </c>
       <c r="P10" t="n">
-        <v>29.8</v>
+        <v>29.9</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.767</v>
+        <v>0.768</v>
       </c>
       <c r="R10" t="n">
         <v>12.4</v>
       </c>
       <c r="S10" t="n">
-        <v>30.2</v>
+        <v>30</v>
       </c>
       <c r="T10" t="n">
-        <v>42.6</v>
+        <v>42.4</v>
       </c>
       <c r="U10" t="n">
-        <v>20.6</v>
+        <v>20.5</v>
       </c>
       <c r="V10" t="n">
         <v>15</v>
@@ -2186,16 +2253,16 @@
         <v>21.8</v>
       </c>
       <c r="AA10" t="n">
-        <v>24</v>
+        <v>24.2</v>
       </c>
       <c r="AB10" t="n">
         <v>107.3</v>
       </c>
       <c r="AC10" t="n">
-        <v>-4.3</v>
+        <v>-4.8</v>
       </c>
       <c r="AD10" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE10" t="n">
         <v>25</v>
@@ -2207,7 +2274,7 @@
         <v>25</v>
       </c>
       <c r="AH10" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AI10" t="n">
         <v>2</v>
@@ -2216,10 +2283,10 @@
         <v>2</v>
       </c>
       <c r="AK10" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AL10" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AM10" t="n">
         <v>14</v>
@@ -2234,31 +2301,31 @@
         <v>2</v>
       </c>
       <c r="AQ10" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AR10" t="n">
         <v>5</v>
       </c>
       <c r="AS10" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="AT10" t="n">
         <v>9</v>
       </c>
       <c r="AU10" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AV10" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="AW10" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AX10" t="n">
         <v>1</v>
       </c>
       <c r="AY10" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AZ10" t="n">
         <v>20</v>
@@ -2282,7 +2349,7 @@
       </c>
       <c r="BF10" t="inlineStr">
         <is>
-          <t>1-25-2008-09</t>
+          <t>2009-01-25</t>
         </is>
       </c>
     </row>
@@ -2299,37 +2366,37 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E11" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="F11" t="n">
         <v>17</v>
       </c>
       <c r="G11" t="n">
-        <v>0.622</v>
+        <v>0.614</v>
       </c>
       <c r="H11" t="n">
         <v>48.3</v>
       </c>
       <c r="I11" t="n">
-        <v>35.4</v>
+        <v>35.3</v>
       </c>
       <c r="J11" t="n">
-        <v>79.2</v>
+        <v>79.3</v>
       </c>
       <c r="K11" t="n">
-        <v>0.447</v>
+        <v>0.445</v>
       </c>
       <c r="L11" t="n">
-        <v>7.4</v>
+        <v>7.3</v>
       </c>
       <c r="M11" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="N11" t="n">
-        <v>0.372</v>
+        <v>0.369</v>
       </c>
       <c r="O11" t="n">
         <v>19.6</v>
@@ -2338,28 +2405,28 @@
         <v>24.3</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.806</v>
+        <v>0.8070000000000001</v>
       </c>
       <c r="R11" t="n">
         <v>10.4</v>
       </c>
       <c r="S11" t="n">
-        <v>32.2</v>
+        <v>32.3</v>
       </c>
       <c r="T11" t="n">
-        <v>42.6</v>
+        <v>42.8</v>
       </c>
       <c r="U11" t="n">
-        <v>20.3</v>
+        <v>20.1</v>
       </c>
       <c r="V11" t="n">
-        <v>14.2</v>
+        <v>14.3</v>
       </c>
       <c r="W11" t="n">
-        <v>6.6</v>
+        <v>6.7</v>
       </c>
       <c r="X11" t="n">
-        <v>3.6</v>
+        <v>3.7</v>
       </c>
       <c r="Y11" t="n">
         <v>5.4</v>
@@ -2368,16 +2435,16 @@
         <v>18.8</v>
       </c>
       <c r="AA11" t="n">
-        <v>21.1</v>
+        <v>21</v>
       </c>
       <c r="AB11" t="n">
-        <v>97.8</v>
+        <v>97.5</v>
       </c>
       <c r="AC11" t="n">
         <v>2.8</v>
       </c>
       <c r="AD11" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE11" t="n">
         <v>7</v>
@@ -2386,31 +2453,31 @@
         <v>9</v>
       </c>
       <c r="AG11" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AH11" t="n">
         <v>17</v>
       </c>
       <c r="AI11" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AJ11" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AK11" t="n">
-        <v>22</v>
+        <v>25</v>
       </c>
       <c r="AL11" t="n">
-        <v>8</v>
+        <v>10</v>
       </c>
       <c r="AM11" t="n">
         <v>9</v>
       </c>
       <c r="AN11" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AO11" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AP11" t="n">
         <v>19</v>
@@ -2419,22 +2486,22 @@
         <v>5</v>
       </c>
       <c r="AR11" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AS11" t="n">
         <v>3</v>
       </c>
       <c r="AT11" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="AU11" t="n">
-        <v>19</v>
+        <v>21</v>
       </c>
       <c r="AV11" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AW11" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AX11" t="n">
         <v>28</v>
@@ -2443,10 +2510,10 @@
         <v>22</v>
       </c>
       <c r="AZ11" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="BA11" t="n">
-        <v>14</v>
+        <v>16</v>
       </c>
       <c r="BB11" t="n">
         <v>19</v>
@@ -2464,7 +2531,7 @@
       </c>
       <c r="BF11" t="inlineStr">
         <is>
-          <t>1-25-2008-09</t>
+          <t>2009-01-25</t>
         </is>
       </c>
     </row>
@@ -2481,16 +2548,16 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>44</v>
+        <v>43</v>
       </c>
       <c r="E12" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="F12" t="n">
         <v>27</v>
       </c>
       <c r="G12" t="n">
-        <v>0.386</v>
+        <v>0.372</v>
       </c>
       <c r="H12" t="n">
         <v>48.7</v>
@@ -2502,7 +2569,7 @@
         <v>86.3</v>
       </c>
       <c r="K12" t="n">
-        <v>0.45</v>
+        <v>0.451</v>
       </c>
       <c r="L12" t="n">
         <v>7.4</v>
@@ -2511,7 +2578,7 @@
         <v>20.3</v>
       </c>
       <c r="N12" t="n">
-        <v>0.363</v>
+        <v>0.366</v>
       </c>
       <c r="O12" t="n">
         <v>19</v>
@@ -2520,19 +2587,19 @@
         <v>23.5</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.8090000000000001</v>
+        <v>0.8080000000000001</v>
       </c>
       <c r="R12" t="n">
-        <v>11.4</v>
+        <v>11.2</v>
       </c>
       <c r="S12" t="n">
         <v>32.5</v>
       </c>
       <c r="T12" t="n">
-        <v>43.9</v>
+        <v>43.7</v>
       </c>
       <c r="U12" t="n">
-        <v>22.9</v>
+        <v>23</v>
       </c>
       <c r="V12" t="n">
         <v>15.2</v>
@@ -2544,31 +2611,31 @@
         <v>5</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.5</v>
+        <v>5.6</v>
       </c>
       <c r="Z12" t="n">
-        <v>23.8</v>
+        <v>23.9</v>
       </c>
       <c r="AA12" t="n">
         <v>21.3</v>
       </c>
       <c r="AB12" t="n">
-        <v>104.1</v>
+        <v>104.3</v>
       </c>
       <c r="AC12" t="n">
-        <v>-2.1</v>
+        <v>-2.3</v>
       </c>
       <c r="AD12" t="n">
-        <v>8</v>
+        <v>11</v>
       </c>
       <c r="AE12" t="n">
+        <v>23</v>
+      </c>
+      <c r="AF12" t="n">
         <v>22</v>
       </c>
-      <c r="AF12" t="n">
-        <v>21</v>
-      </c>
       <c r="AG12" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AH12" t="n">
         <v>3</v>
@@ -2583,7 +2650,7 @@
         <v>17</v>
       </c>
       <c r="AL12" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AM12" t="n">
         <v>8</v>
@@ -2592,10 +2659,10 @@
         <v>16</v>
       </c>
       <c r="AO12" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AP12" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AQ12" t="n">
         <v>4</v>
@@ -2607,19 +2674,19 @@
         <v>2</v>
       </c>
       <c r="AT12" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AU12" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AV12" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AW12" t="n">
         <v>20</v>
       </c>
       <c r="AX12" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AY12" t="n">
         <v>26</v>
@@ -2634,7 +2701,7 @@
         <v>4</v>
       </c>
       <c r="BC12" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="BD12" t="n">
         <v>10</v>
@@ -2646,7 +2713,7 @@
       </c>
       <c r="BF12" t="inlineStr">
         <is>
-          <t>1-25-2008-09</t>
+          <t>2009-01-25</t>
         </is>
       </c>
     </row>
@@ -2663,16 +2730,16 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E13" t="n">
         <v>10</v>
       </c>
       <c r="F13" t="n">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="G13" t="n">
-        <v>0.233</v>
+        <v>0.238</v>
       </c>
       <c r="H13" t="n">
         <v>48.7</v>
@@ -2681,73 +2748,73 @@
         <v>35.4</v>
       </c>
       <c r="J13" t="n">
-        <v>82.5</v>
+        <v>82.40000000000001</v>
       </c>
       <c r="K13" t="n">
-        <v>0.429</v>
+        <v>0.43</v>
       </c>
       <c r="L13" t="n">
-        <v>5.4</v>
+        <v>5.3</v>
       </c>
       <c r="M13" t="n">
         <v>16.4</v>
       </c>
       <c r="N13" t="n">
-        <v>0.327</v>
+        <v>0.324</v>
       </c>
       <c r="O13" t="n">
         <v>17.3</v>
       </c>
       <c r="P13" t="n">
-        <v>23.1</v>
+        <v>23</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.749</v>
+        <v>0.751</v>
       </c>
       <c r="R13" t="n">
-        <v>12.3</v>
+        <v>12.2</v>
       </c>
       <c r="S13" t="n">
-        <v>29.5</v>
+        <v>29.4</v>
       </c>
       <c r="T13" t="n">
-        <v>41.7</v>
+        <v>41.6</v>
       </c>
       <c r="U13" t="n">
-        <v>19.9</v>
+        <v>19.7</v>
       </c>
       <c r="V13" t="n">
-        <v>14.9</v>
+        <v>14.8</v>
       </c>
       <c r="W13" t="n">
         <v>7</v>
       </c>
       <c r="X13" t="n">
-        <v>6.5</v>
+        <v>6.6</v>
       </c>
       <c r="Y13" t="n">
         <v>5.7</v>
       </c>
       <c r="Z13" t="n">
-        <v>21.2</v>
+        <v>21.3</v>
       </c>
       <c r="AA13" t="n">
-        <v>19.9</v>
+        <v>19.8</v>
       </c>
       <c r="AB13" t="n">
         <v>93.40000000000001</v>
       </c>
       <c r="AC13" t="n">
-        <v>-7.1</v>
+        <v>-6.9</v>
       </c>
       <c r="AD13" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AE13" t="n">
         <v>27</v>
       </c>
       <c r="AF13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AG13" t="n">
         <v>27</v>
@@ -2756,7 +2823,7 @@
         <v>1</v>
       </c>
       <c r="AI13" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AJ13" t="n">
         <v>8</v>
@@ -2768,10 +2835,10 @@
         <v>24</v>
       </c>
       <c r="AM13" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AN13" t="n">
-        <v>28</v>
+        <v>30</v>
       </c>
       <c r="AO13" t="n">
         <v>26</v>
@@ -2780,25 +2847,25 @@
         <v>24</v>
       </c>
       <c r="AQ13" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AR13" t="n">
         <v>7</v>
       </c>
       <c r="AS13" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AT13" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AU13" t="n">
-        <v>25</v>
+        <v>27</v>
       </c>
       <c r="AV13" t="n">
         <v>18</v>
       </c>
       <c r="AW13" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AX13" t="n">
         <v>2</v>
@@ -2807,13 +2874,13 @@
         <v>28</v>
       </c>
       <c r="AZ13" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BA13" t="n">
         <v>25</v>
       </c>
       <c r="BB13" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="BC13" t="n">
         <v>29</v>
@@ -2828,7 +2895,7 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>1-25-2008-09</t>
+          <t>2009-01-25</t>
         </is>
       </c>
     </row>
@@ -2860,10 +2927,10 @@
         <v>48</v>
       </c>
       <c r="I14" t="n">
-        <v>39.9</v>
+        <v>40</v>
       </c>
       <c r="J14" t="n">
-        <v>83.5</v>
+        <v>83.8</v>
       </c>
       <c r="K14" t="n">
         <v>0.477</v>
@@ -2872,34 +2939,34 @@
         <v>7.1</v>
       </c>
       <c r="M14" t="n">
-        <v>18.7</v>
+        <v>18.6</v>
       </c>
       <c r="N14" t="n">
-        <v>0.377</v>
+        <v>0.381</v>
       </c>
       <c r="O14" t="n">
-        <v>21.1</v>
+        <v>20.8</v>
       </c>
       <c r="P14" t="n">
-        <v>27.4</v>
+        <v>27.1</v>
       </c>
       <c r="Q14" t="n">
-        <v>0.769</v>
+        <v>0.767</v>
       </c>
       <c r="R14" t="n">
-        <v>12.3</v>
+        <v>12.4</v>
       </c>
       <c r="S14" t="n">
-        <v>31.5</v>
+        <v>31.6</v>
       </c>
       <c r="T14" t="n">
-        <v>43.8</v>
+        <v>44</v>
       </c>
       <c r="U14" t="n">
         <v>23.5</v>
       </c>
       <c r="V14" t="n">
-        <v>13.8</v>
+        <v>13.7</v>
       </c>
       <c r="W14" t="n">
         <v>8.6</v>
@@ -2908,31 +2975,31 @@
         <v>5.2</v>
       </c>
       <c r="Y14" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Z14" t="n">
-        <v>19.9</v>
+        <v>20</v>
       </c>
       <c r="AA14" t="n">
-        <v>22.8</v>
+        <v>22.6</v>
       </c>
       <c r="AB14" t="n">
-        <v>107.9</v>
+        <v>107.8</v>
       </c>
       <c r="AC14" t="n">
-        <v>8.6</v>
+        <v>8.699999999999999</v>
       </c>
       <c r="AD14" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AE14" t="n">
         <v>2</v>
       </c>
       <c r="AF14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AG14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AH14" t="n">
         <v>29</v>
@@ -2941,10 +3008,10 @@
         <v>1</v>
       </c>
       <c r="AJ14" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AK14" t="n">
-        <v>4</v>
+        <v>3</v>
       </c>
       <c r="AL14" t="n">
         <v>11</v>
@@ -2953,7 +3020,7 @@
         <v>13</v>
       </c>
       <c r="AN14" t="n">
-        <v>8</v>
+        <v>5</v>
       </c>
       <c r="AO14" t="n">
         <v>4</v>
@@ -2962,7 +3029,7 @@
         <v>4</v>
       </c>
       <c r="AQ14" t="n">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="AR14" t="n">
         <v>6</v>
@@ -2971,13 +3038,13 @@
         <v>7</v>
       </c>
       <c r="AT14" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AU14" t="n">
         <v>2</v>
       </c>
       <c r="AV14" t="n">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="AW14" t="n">
         <v>3</v>
@@ -2989,7 +3056,7 @@
         <v>10</v>
       </c>
       <c r="AZ14" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="BA14" t="n">
         <v>5</v>
@@ -3010,7 +3077,7 @@
       </c>
       <c r="BF14" t="inlineStr">
         <is>
-          <t>1-25-2008-09</t>
+          <t>2009-01-25</t>
         </is>
       </c>
     </row>
@@ -3105,7 +3172,7 @@
         <v>-6.6</v>
       </c>
       <c r="AD15" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AE15" t="n">
         <v>26</v>
@@ -3117,13 +3184,13 @@
         <v>26</v>
       </c>
       <c r="AH15" t="n">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="AI15" t="n">
         <v>29</v>
       </c>
       <c r="AJ15" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AK15" t="n">
         <v>18</v>
@@ -3135,7 +3202,7 @@
         <v>27</v>
       </c>
       <c r="AN15" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AO15" t="n">
         <v>12</v>
@@ -3144,7 +3211,7 @@
         <v>8</v>
       </c>
       <c r="AQ15" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AR15" t="n">
         <v>25</v>
@@ -3165,7 +3232,7 @@
         <v>9</v>
       </c>
       <c r="AX15" t="n">
-        <v>23</v>
+        <v>24</v>
       </c>
       <c r="AY15" t="n">
         <v>17</v>
@@ -3174,7 +3241,7 @@
         <v>19</v>
       </c>
       <c r="BA15" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="BB15" t="n">
         <v>29</v>
@@ -3192,7 +3259,7 @@
       </c>
       <c r="BF15" t="inlineStr">
         <is>
-          <t>1-25-2008-09</t>
+          <t>2009-01-25</t>
         </is>
       </c>
     </row>
@@ -3287,13 +3354,13 @@
         <v>-0.1</v>
       </c>
       <c r="AD16" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AE16" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AF16" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="AG16" t="n">
         <v>15</v>
@@ -3323,13 +3390,13 @@
         <v>27</v>
       </c>
       <c r="AP16" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AQ16" t="n">
         <v>29</v>
       </c>
       <c r="AR16" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AS16" t="n">
         <v>23</v>
@@ -3338,7 +3405,7 @@
         <v>24</v>
       </c>
       <c r="AU16" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AV16" t="n">
         <v>3</v>
@@ -3347,13 +3414,13 @@
         <v>5</v>
       </c>
       <c r="AX16" t="n">
-        <v>8</v>
+        <v>7</v>
       </c>
       <c r="AY16" t="n">
         <v>9</v>
       </c>
       <c r="AZ16" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="BA16" t="n">
         <v>26</v>
@@ -3374,7 +3441,7 @@
       </c>
       <c r="BF16" t="inlineStr">
         <is>
-          <t>1-25-2008-09</t>
+          <t>2009-01-25</t>
         </is>
       </c>
     </row>
@@ -3391,16 +3458,16 @@
         </is>
       </c>
       <c r="D17" t="n">
-        <v>46</v>
+        <v>47</v>
       </c>
       <c r="E17" t="n">
         <v>22</v>
       </c>
       <c r="F17" t="n">
-        <v>24</v>
+        <v>25</v>
       </c>
       <c r="G17" t="n">
-        <v>0.478</v>
+        <v>0.468</v>
       </c>
       <c r="H17" t="n">
         <v>48.3</v>
@@ -3409,7 +3476,7 @@
         <v>36.6</v>
       </c>
       <c r="J17" t="n">
-        <v>81.8</v>
+        <v>81.7</v>
       </c>
       <c r="K17" t="n">
         <v>0.448</v>
@@ -3421,13 +3488,13 @@
         <v>16</v>
       </c>
       <c r="N17" t="n">
-        <v>0.354</v>
+        <v>0.355</v>
       </c>
       <c r="O17" t="n">
-        <v>19.6</v>
+        <v>19.5</v>
       </c>
       <c r="P17" t="n">
-        <v>25.1</v>
+        <v>25</v>
       </c>
       <c r="Q17" t="n">
         <v>0.78</v>
@@ -3436,16 +3503,16 @@
         <v>12.4</v>
       </c>
       <c r="S17" t="n">
-        <v>29.5</v>
+        <v>29.3</v>
       </c>
       <c r="T17" t="n">
-        <v>41.9</v>
+        <v>41.7</v>
       </c>
       <c r="U17" t="n">
         <v>21.3</v>
       </c>
       <c r="V17" t="n">
-        <v>14.3</v>
+        <v>14.4</v>
       </c>
       <c r="W17" t="n">
         <v>7.1</v>
@@ -3457,16 +3524,16 @@
         <v>4.8</v>
       </c>
       <c r="Z17" t="n">
-        <v>23.9</v>
+        <v>24</v>
       </c>
       <c r="AA17" t="n">
-        <v>22.6</v>
+        <v>22.5</v>
       </c>
       <c r="AB17" t="n">
-        <v>98.5</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AC17" t="n">
-        <v>0.5</v>
+        <v>0.2</v>
       </c>
       <c r="AD17" t="n">
         <v>1</v>
@@ -3475,13 +3542,13 @@
         <v>16</v>
       </c>
       <c r="AF17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AG17" t="n">
         <v>17</v>
       </c>
       <c r="AH17" t="n">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="AI17" t="n">
         <v>15</v>
@@ -3502,10 +3569,10 @@
         <v>21</v>
       </c>
       <c r="AO17" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AP17" t="n">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="AQ17" t="n">
         <v>9</v>
@@ -3514,19 +3581,19 @@
         <v>4</v>
       </c>
       <c r="AS17" t="n">
-        <v>21</v>
+        <v>24</v>
       </c>
       <c r="AT17" t="n">
         <v>13</v>
       </c>
       <c r="AU17" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AV17" t="n">
         <v>16</v>
       </c>
       <c r="AW17" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AX17" t="n">
         <v>29</v>
@@ -3544,7 +3611,7 @@
         <v>17</v>
       </c>
       <c r="BC17" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="BD17" t="n">
         <v>10</v>
@@ -3556,7 +3623,7 @@
       </c>
       <c r="BF17" t="inlineStr">
         <is>
-          <t>1-25-2008-09</t>
+          <t>2009-01-25</t>
         </is>
       </c>
     </row>
@@ -3573,25 +3640,25 @@
         </is>
       </c>
       <c r="D18" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E18" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="F18" t="n">
         <v>27</v>
       </c>
       <c r="G18" t="n">
-        <v>0.357</v>
+        <v>0.341</v>
       </c>
       <c r="H18" t="n">
-        <v>48.6</v>
+        <v>48.5</v>
       </c>
       <c r="I18" t="n">
-        <v>37</v>
+        <v>36.9</v>
       </c>
       <c r="J18" t="n">
-        <v>83.90000000000001</v>
+        <v>83.7</v>
       </c>
       <c r="K18" t="n">
         <v>0.441</v>
@@ -3603,70 +3670,70 @@
         <v>16.6</v>
       </c>
       <c r="N18" t="n">
-        <v>0.347</v>
+        <v>0.349</v>
       </c>
       <c r="O18" t="n">
-        <v>19</v>
+        <v>18.9</v>
       </c>
       <c r="P18" t="n">
-        <v>25</v>
+        <v>24.9</v>
       </c>
       <c r="Q18" t="n">
-        <v>0.759</v>
+        <v>0.758</v>
       </c>
       <c r="R18" t="n">
-        <v>12.7</v>
+        <v>12.6</v>
       </c>
       <c r="S18" t="n">
-        <v>29.7</v>
+        <v>29.6</v>
       </c>
       <c r="T18" t="n">
-        <v>42.4</v>
+        <v>42.3</v>
       </c>
       <c r="U18" t="n">
         <v>20.4</v>
       </c>
       <c r="V18" t="n">
-        <v>14.2</v>
+        <v>14.1</v>
       </c>
       <c r="W18" t="n">
         <v>6.4</v>
       </c>
       <c r="X18" t="n">
-        <v>4.1</v>
+        <v>4.2</v>
       </c>
       <c r="Y18" t="n">
-        <v>6.6</v>
+        <v>6.5</v>
       </c>
       <c r="Z18" t="n">
-        <v>21.8</v>
+        <v>21.9</v>
       </c>
       <c r="AA18" t="n">
         <v>20.7</v>
       </c>
       <c r="AB18" t="n">
-        <v>98.7</v>
+        <v>98.40000000000001</v>
       </c>
       <c r="AC18" t="n">
-        <v>-3.2</v>
+        <v>-3.3</v>
       </c>
       <c r="AD18" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AE18" t="n">
         <v>24</v>
       </c>
       <c r="AF18" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AG18" t="n">
         <v>24</v>
       </c>
       <c r="AH18" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AI18" t="n">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AJ18" t="n">
         <v>5</v>
@@ -3681,7 +3748,7 @@
         <v>19</v>
       </c>
       <c r="AN18" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AO18" t="n">
         <v>17</v>
@@ -3702,10 +3769,10 @@
         <v>10</v>
       </c>
       <c r="AU18" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AV18" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="AW18" t="n">
         <v>28</v>
@@ -3723,7 +3790,7 @@
         <v>20</v>
       </c>
       <c r="BB18" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="BC18" t="n">
         <v>23</v>
@@ -3738,7 +3805,7 @@
       </c>
       <c r="BF18" t="inlineStr">
         <is>
-          <t>1-25-2008-09</t>
+          <t>2009-01-25</t>
         </is>
       </c>
     </row>
@@ -3833,7 +3900,7 @@
         <v>-2.9</v>
       </c>
       <c r="AD19" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AE19" t="n">
         <v>18</v>
@@ -3845,7 +3912,7 @@
         <v>18</v>
       </c>
       <c r="AH19" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AI19" t="n">
         <v>25</v>
@@ -3860,10 +3927,10 @@
         <v>5</v>
       </c>
       <c r="AM19" t="n">
-        <v>6</v>
+        <v>5</v>
       </c>
       <c r="AN19" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AO19" t="n">
         <v>8</v>
@@ -3881,7 +3948,7 @@
         <v>20</v>
       </c>
       <c r="AT19" t="n">
-        <v>20</v>
+        <v>21</v>
       </c>
       <c r="AU19" t="n">
         <v>29</v>
@@ -3896,16 +3963,16 @@
         <v>20</v>
       </c>
       <c r="AY19" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AZ19" t="n">
         <v>26</v>
       </c>
       <c r="BA19" t="n">
+        <v>14</v>
+      </c>
+      <c r="BB19" t="n">
         <v>15</v>
-      </c>
-      <c r="BB19" t="n">
-        <v>17</v>
       </c>
       <c r="BC19" t="n">
         <v>22</v>
@@ -3920,7 +3987,7 @@
       </c>
       <c r="BF19" t="inlineStr">
         <is>
-          <t>1-25-2008-09</t>
+          <t>2009-01-25</t>
         </is>
       </c>
     </row>
@@ -4021,7 +4088,7 @@
         <v>8</v>
       </c>
       <c r="AF20" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AG20" t="n">
         <v>7</v>
@@ -4036,16 +4103,16 @@
         <v>29</v>
       </c>
       <c r="AK20" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="AL20" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AM20" t="n">
         <v>11</v>
       </c>
       <c r="AN20" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AO20" t="n">
         <v>23</v>
@@ -4066,7 +4133,7 @@
         <v>29</v>
       </c>
       <c r="AU20" t="n">
-        <v>26</v>
+        <v>25</v>
       </c>
       <c r="AV20" t="n">
         <v>4</v>
@@ -4075,7 +4142,7 @@
         <v>12</v>
       </c>
       <c r="AX20" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AY20" t="n">
         <v>1</v>
@@ -4084,7 +4151,7 @@
         <v>14</v>
       </c>
       <c r="BA20" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="BB20" t="n">
         <v>24</v>
@@ -4102,7 +4169,7 @@
       </c>
       <c r="BF20" t="inlineStr">
         <is>
-          <t>1-25-2008-09</t>
+          <t>2009-01-25</t>
         </is>
       </c>
     </row>
@@ -4197,19 +4264,19 @@
         <v>-2.7</v>
       </c>
       <c r="AD21" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AE21" t="n">
         <v>19</v>
       </c>
       <c r="AF21" t="n">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="AG21" t="n">
         <v>19</v>
       </c>
       <c r="AH21" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI21" t="n">
         <v>7</v>
@@ -4251,7 +4318,7 @@
         <v>10</v>
       </c>
       <c r="AV21" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="AW21" t="n">
         <v>11</v>
@@ -4263,7 +4330,7 @@
         <v>21</v>
       </c>
       <c r="AZ21" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="BA21" t="n">
         <v>29</v>
@@ -4284,7 +4351,7 @@
       </c>
       <c r="BF21" t="inlineStr">
         <is>
-          <t>1-25-2008-09</t>
+          <t>2009-01-25</t>
         </is>
       </c>
     </row>
@@ -4379,19 +4446,19 @@
         <v>-6.7</v>
       </c>
       <c r="AD22" t="n">
-        <v>8</v>
+        <v>4</v>
       </c>
       <c r="AE22" t="n">
         <v>29</v>
       </c>
       <c r="AF22" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AG22" t="n">
         <v>30</v>
       </c>
       <c r="AH22" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AI22" t="n">
         <v>17</v>
@@ -4415,10 +4482,10 @@
         <v>11</v>
       </c>
       <c r="AP22" t="n">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="AQ22" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AR22" t="n">
         <v>10</v>
@@ -4427,13 +4494,13 @@
         <v>11</v>
       </c>
       <c r="AT22" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="AU22" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AV22" t="n">
-        <v>29</v>
+        <v>30</v>
       </c>
       <c r="AW22" t="n">
         <v>22</v>
@@ -4448,7 +4515,7 @@
         <v>16</v>
       </c>
       <c r="BA22" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BB22" t="n">
         <v>25</v>
@@ -4466,7 +4533,7 @@
       </c>
       <c r="BF22" t="inlineStr">
         <is>
-          <t>1-25-2008-09</t>
+          <t>2009-01-25</t>
         </is>
       </c>
     </row>
@@ -4561,7 +4628,7 @@
         <v>7.8</v>
       </c>
       <c r="AD23" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AE23" t="n">
         <v>4</v>
@@ -4573,16 +4640,16 @@
         <v>4</v>
       </c>
       <c r="AH23" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI23" t="n">
         <v>22</v>
       </c>
       <c r="AJ23" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AK23" t="n">
-        <v>9</v>
+        <v>8</v>
       </c>
       <c r="AL23" t="n">
         <v>2</v>
@@ -4597,7 +4664,7 @@
         <v>13</v>
       </c>
       <c r="AP23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AQ23" t="n">
         <v>30</v>
@@ -4609,22 +4676,22 @@
         <v>1</v>
       </c>
       <c r="AT23" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AU23" t="n">
         <v>28</v>
       </c>
       <c r="AV23" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AW23" t="n">
         <v>14</v>
       </c>
       <c r="AX23" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AY23" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AZ23" t="n">
         <v>9</v>
@@ -4648,7 +4715,7 @@
       </c>
       <c r="BF23" t="inlineStr">
         <is>
-          <t>1-25-2008-09</t>
+          <t>2009-01-25</t>
         </is>
       </c>
     </row>
@@ -4743,7 +4810,7 @@
         <v>0.7</v>
       </c>
       <c r="AD24" t="n">
-        <v>23</v>
+        <v>20</v>
       </c>
       <c r="AE24" t="n">
         <v>17</v>
@@ -4755,10 +4822,10 @@
         <v>16</v>
       </c>
       <c r="AH24" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AI24" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AJ24" t="n">
         <v>14</v>
@@ -4779,10 +4846,10 @@
         <v>21</v>
       </c>
       <c r="AP24" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AQ24" t="n">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AR24" t="n">
         <v>2</v>
@@ -4794,7 +4861,7 @@
         <v>5</v>
       </c>
       <c r="AU24" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AV24" t="n">
         <v>24</v>
@@ -4809,16 +4876,16 @@
         <v>15</v>
       </c>
       <c r="AZ24" t="n">
-        <v>7</v>
+        <v>8</v>
       </c>
       <c r="BA24" t="n">
         <v>19</v>
       </c>
       <c r="BB24" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="BC24" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="BD24" t="n">
         <v>10</v>
@@ -4830,7 +4897,7 @@
       </c>
       <c r="BF24" t="inlineStr">
         <is>
-          <t>1-25-2008-09</t>
+          <t>2009-01-25</t>
         </is>
       </c>
     </row>
@@ -4847,94 +4914,94 @@
         </is>
       </c>
       <c r="D25" t="n">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="E25" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="F25" t="n">
         <v>18</v>
       </c>
       <c r="G25" t="n">
-        <v>0.571</v>
+        <v>0.5610000000000001</v>
       </c>
       <c r="H25" t="n">
         <v>48.2</v>
       </c>
       <c r="I25" t="n">
-        <v>38.3</v>
+        <v>38.4</v>
       </c>
       <c r="J25" t="n">
-        <v>77.2</v>
+        <v>77.5</v>
       </c>
       <c r="K25" t="n">
-        <v>0.496</v>
+        <v>0.495</v>
       </c>
       <c r="L25" t="n">
         <v>6.7</v>
       </c>
       <c r="M25" t="n">
-        <v>17.3</v>
+        <v>17.5</v>
       </c>
       <c r="N25" t="n">
-        <v>0.386</v>
+        <v>0.384</v>
       </c>
       <c r="O25" t="n">
-        <v>20.5</v>
+        <v>20.4</v>
       </c>
       <c r="P25" t="n">
-        <v>27.1</v>
+        <v>27</v>
       </c>
       <c r="Q25" t="n">
-        <v>0.756</v>
+        <v>0.754</v>
       </c>
       <c r="R25" t="n">
-        <v>9.6</v>
+        <v>9.699999999999999</v>
       </c>
       <c r="S25" t="n">
-        <v>31.5</v>
+        <v>31.3</v>
       </c>
       <c r="T25" t="n">
-        <v>41</v>
+        <v>41.1</v>
       </c>
       <c r="U25" t="n">
         <v>21.6</v>
       </c>
       <c r="V25" t="n">
-        <v>16.5</v>
+        <v>16.4</v>
       </c>
       <c r="W25" t="n">
         <v>6.3</v>
       </c>
       <c r="X25" t="n">
-        <v>4.9</v>
+        <v>5</v>
       </c>
       <c r="Y25" t="n">
         <v>4.1</v>
       </c>
       <c r="Z25" t="n">
-        <v>20.4</v>
+        <v>20.3</v>
       </c>
       <c r="AA25" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="AB25" t="n">
         <v>103.8</v>
       </c>
       <c r="AC25" t="n">
-        <v>0.7</v>
+        <v>0.6</v>
       </c>
       <c r="AD25" t="n">
-        <v>23</v>
+        <v>28</v>
       </c>
       <c r="AE25" t="n">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="AF25" t="n">
         <v>11</v>
       </c>
       <c r="AG25" t="n">
-        <v>11</v>
+        <v>14</v>
       </c>
       <c r="AH25" t="n">
         <v>20</v>
@@ -4949,22 +5016,22 @@
         <v>1</v>
       </c>
       <c r="AL25" t="n">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="AM25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AN25" t="n">
-        <v>5</v>
+        <v>4</v>
       </c>
       <c r="AO25" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AP25" t="n">
         <v>5</v>
       </c>
       <c r="AQ25" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AR25" t="n">
         <v>27</v>
@@ -4973,22 +5040,22 @@
         <v>8</v>
       </c>
       <c r="AT25" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="AU25" t="n">
         <v>9</v>
       </c>
       <c r="AV25" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AW25" t="n">
         <v>29</v>
       </c>
       <c r="AX25" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AY25" t="n">
-        <v>6</v>
+        <v>7</v>
       </c>
       <c r="AZ25" t="n">
         <v>10</v>
@@ -5000,7 +5067,7 @@
         <v>5</v>
       </c>
       <c r="BC25" t="n">
-        <v>12</v>
+        <v>14</v>
       </c>
       <c r="BD25" t="n">
         <v>10</v>
@@ -5012,7 +5079,7 @@
       </c>
       <c r="BF25" t="inlineStr">
         <is>
-          <t>1-25-2008-09</t>
+          <t>2009-01-25</t>
         </is>
       </c>
     </row>
@@ -5029,61 +5096,61 @@
         </is>
       </c>
       <c r="D26" t="n">
-        <v>42</v>
+        <v>43</v>
       </c>
       <c r="E26" t="n">
         <v>26</v>
       </c>
       <c r="F26" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="G26" t="n">
-        <v>0.619</v>
+        <v>0.605</v>
       </c>
       <c r="H26" t="n">
         <v>48.5</v>
       </c>
       <c r="I26" t="n">
-        <v>36</v>
+        <v>35.8</v>
       </c>
       <c r="J26" t="n">
-        <v>78.8</v>
+        <v>78.90000000000001</v>
       </c>
       <c r="K26" t="n">
-        <v>0.457</v>
+        <v>0.454</v>
       </c>
       <c r="L26" t="n">
         <v>7.4</v>
       </c>
       <c r="M26" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="N26" t="n">
-        <v>0.378</v>
+        <v>0.379</v>
       </c>
       <c r="O26" t="n">
-        <v>19.2</v>
+        <v>19</v>
       </c>
       <c r="P26" t="n">
-        <v>25.1</v>
+        <v>24.8</v>
       </c>
       <c r="Q26" t="n">
-        <v>0.766</v>
+        <v>0.764</v>
       </c>
       <c r="R26" t="n">
         <v>13.2</v>
       </c>
       <c r="S26" t="n">
-        <v>27.7</v>
+        <v>27.8</v>
       </c>
       <c r="T26" t="n">
         <v>40.9</v>
       </c>
       <c r="U26" t="n">
-        <v>20.3</v>
+        <v>20.2</v>
       </c>
       <c r="V26" t="n">
-        <v>12.7</v>
+        <v>12.8</v>
       </c>
       <c r="W26" t="n">
         <v>7</v>
@@ -5095,28 +5162,28 @@
         <v>3.7</v>
       </c>
       <c r="Z26" t="n">
-        <v>20.9</v>
+        <v>20.8</v>
       </c>
       <c r="AA26" t="n">
-        <v>21.7</v>
+        <v>21.6</v>
       </c>
       <c r="AB26" t="n">
-        <v>98.59999999999999</v>
+        <v>98.09999999999999</v>
       </c>
       <c r="AC26" t="n">
-        <v>3.5</v>
+        <v>3</v>
       </c>
       <c r="AD26" t="n">
-        <v>23</v>
+        <v>11</v>
       </c>
       <c r="AE26" t="n">
         <v>8</v>
       </c>
       <c r="AF26" t="n">
-        <v>8</v>
+        <v>9</v>
       </c>
       <c r="AG26" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="AH26" t="n">
         <v>10</v>
@@ -5128,22 +5195,22 @@
         <v>21</v>
       </c>
       <c r="AK26" t="n">
-        <v>12</v>
+        <v>13</v>
       </c>
       <c r="AL26" t="n">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="AM26" t="n">
         <v>10</v>
       </c>
       <c r="AN26" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AO26" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AP26" t="n">
-        <v>13</v>
+        <v>16</v>
       </c>
       <c r="AQ26" t="n">
         <v>16</v>
@@ -5158,7 +5225,7 @@
         <v>19</v>
       </c>
       <c r="AU26" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AV26" t="n">
         <v>5</v>
@@ -5170,19 +5237,19 @@
         <v>12</v>
       </c>
       <c r="AY26" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="AZ26" t="n">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="BA26" t="n">
         <v>11</v>
       </c>
       <c r="BB26" t="n">
-        <v>16</v>
+        <v>18</v>
       </c>
       <c r="BC26" t="n">
-        <v>6</v>
+        <v>8</v>
       </c>
       <c r="BD26" t="n">
         <v>10</v>
@@ -5194,7 +5261,7 @@
       </c>
       <c r="BF26" t="inlineStr">
         <is>
-          <t>1-25-2008-09</t>
+          <t>2009-01-25</t>
         </is>
       </c>
     </row>
@@ -5211,16 +5278,16 @@
         </is>
       </c>
       <c r="D27" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E27" t="n">
         <v>10</v>
       </c>
       <c r="F27" t="n">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="G27" t="n">
-        <v>0.222</v>
+        <v>0.227</v>
       </c>
       <c r="H27" t="n">
         <v>48.7</v>
@@ -5235,19 +5302,19 @@
         <v>0.445</v>
       </c>
       <c r="L27" t="n">
-        <v>6.2</v>
+        <v>6.1</v>
       </c>
       <c r="M27" t="n">
-        <v>18</v>
+        <v>17.8</v>
       </c>
       <c r="N27" t="n">
-        <v>0.347</v>
+        <v>0.344</v>
       </c>
       <c r="O27" t="n">
-        <v>20.2</v>
+        <v>20.3</v>
       </c>
       <c r="P27" t="n">
-        <v>25.1</v>
+        <v>25.3</v>
       </c>
       <c r="Q27" t="n">
         <v>0.804</v>
@@ -5256,10 +5323,10 @@
         <v>10.3</v>
       </c>
       <c r="S27" t="n">
-        <v>28.9</v>
+        <v>29</v>
       </c>
       <c r="T27" t="n">
-        <v>39.2</v>
+        <v>39.4</v>
       </c>
       <c r="U27" t="n">
         <v>20.1</v>
@@ -5280,28 +5347,28 @@
         <v>23.7</v>
       </c>
       <c r="AA27" t="n">
-        <v>21.7</v>
+        <v>21.8</v>
       </c>
       <c r="AB27" t="n">
-        <v>98.8</v>
+        <v>98.90000000000001</v>
       </c>
       <c r="AC27" t="n">
-        <v>-8.9</v>
+        <v>-8.800000000000001</v>
       </c>
       <c r="AD27" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE27" t="n">
         <v>27</v>
       </c>
       <c r="AF27" t="n">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="AG27" t="n">
         <v>28</v>
       </c>
       <c r="AH27" t="n">
-        <v>6</v>
+        <v>4</v>
       </c>
       <c r="AI27" t="n">
         <v>19</v>
@@ -5310,37 +5377,37 @@
         <v>12</v>
       </c>
       <c r="AK27" t="n">
-        <v>25</v>
+        <v>24</v>
       </c>
       <c r="AL27" t="n">
-        <v>18</v>
+        <v>20</v>
       </c>
       <c r="AM27" t="n">
-        <v>15</v>
+        <v>16</v>
       </c>
       <c r="AN27" t="n">
-        <v>22</v>
+        <v>23</v>
       </c>
       <c r="AO27" t="n">
         <v>7</v>
       </c>
       <c r="AP27" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="AQ27" t="n">
         <v>6</v>
       </c>
       <c r="AR27" t="n">
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="AS27" t="n">
         <v>26</v>
       </c>
       <c r="AT27" t="n">
-        <v>27</v>
+        <v>26</v>
       </c>
       <c r="AU27" t="n">
-        <v>23</v>
+        <v>21</v>
       </c>
       <c r="AV27" t="n">
         <v>27</v>
@@ -5358,7 +5425,7 @@
         <v>28</v>
       </c>
       <c r="BA27" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="BB27" t="n">
         <v>13</v>
@@ -5376,7 +5443,7 @@
       </c>
       <c r="BF27" t="inlineStr">
         <is>
-          <t>1-25-2008-09</t>
+          <t>2009-01-25</t>
         </is>
       </c>
     </row>
@@ -5393,55 +5460,55 @@
         </is>
       </c>
       <c r="D28" t="n">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="E28" t="n">
         <v>29</v>
       </c>
       <c r="F28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="G28" t="n">
-        <v>0.674</v>
+        <v>0.6899999999999999</v>
       </c>
       <c r="H28" t="n">
         <v>48.7</v>
       </c>
       <c r="I28" t="n">
-        <v>36.7</v>
+        <v>36.8</v>
       </c>
       <c r="J28" t="n">
-        <v>79.40000000000001</v>
+        <v>79.2</v>
       </c>
       <c r="K28" t="n">
-        <v>0.462</v>
+        <v>0.464</v>
       </c>
       <c r="L28" t="n">
         <v>8.1</v>
       </c>
       <c r="M28" t="n">
-        <v>20.7</v>
+        <v>20.6</v>
       </c>
       <c r="N28" t="n">
-        <v>0.391</v>
+        <v>0.395</v>
       </c>
       <c r="O28" t="n">
         <v>15.1</v>
       </c>
       <c r="P28" t="n">
-        <v>19.8</v>
+        <v>19.9</v>
       </c>
       <c r="Q28" t="n">
-        <v>0.763</v>
+        <v>0.761</v>
       </c>
       <c r="R28" t="n">
         <v>8.699999999999999</v>
       </c>
       <c r="S28" t="n">
-        <v>31.6</v>
+        <v>31.7</v>
       </c>
       <c r="T28" t="n">
-        <v>40.3</v>
+        <v>40.4</v>
       </c>
       <c r="U28" t="n">
         <v>21.8</v>
@@ -5450,28 +5517,28 @@
         <v>12.1</v>
       </c>
       <c r="W28" t="n">
-        <v>5.7</v>
+        <v>5.5</v>
       </c>
       <c r="X28" t="n">
-        <v>4.3</v>
+        <v>4.4</v>
       </c>
       <c r="Y28" t="n">
-        <v>4.2</v>
+        <v>4.1</v>
       </c>
       <c r="Z28" t="n">
-        <v>18.5</v>
+        <v>18.3</v>
       </c>
       <c r="AA28" t="n">
-        <v>18.6</v>
+        <v>18.7</v>
       </c>
       <c r="AB28" t="n">
-        <v>96.59999999999999</v>
+        <v>96.90000000000001</v>
       </c>
       <c r="AC28" t="n">
-        <v>2.9</v>
+        <v>3.3</v>
       </c>
       <c r="AD28" t="n">
-        <v>15</v>
+        <v>20</v>
       </c>
       <c r="AE28" t="n">
         <v>5</v>
@@ -5486,10 +5553,10 @@
         <v>1</v>
       </c>
       <c r="AI28" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AJ28" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="AK28" t="n">
         <v>7</v>
@@ -5498,10 +5565,10 @@
         <v>3</v>
       </c>
       <c r="AM28" t="n">
-        <v>5</v>
+        <v>6</v>
       </c>
       <c r="AN28" t="n">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c r="AO28" t="n">
         <v>30</v>
@@ -5525,16 +5592,16 @@
         <v>6</v>
       </c>
       <c r="AV28" t="n">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="AW28" t="n">
         <v>30</v>
       </c>
       <c r="AX28" t="n">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="AY28" t="n">
-        <v>7</v>
+        <v>6</v>
       </c>
       <c r="AZ28" t="n">
         <v>1</v>
@@ -5543,10 +5610,10 @@
         <v>30</v>
       </c>
       <c r="BB28" t="n">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="BC28" t="n">
-        <v>8</v>
+        <v>6</v>
       </c>
       <c r="BD28" t="n">
         <v>10</v>
@@ -5558,7 +5625,7 @@
       </c>
       <c r="BF28" t="inlineStr">
         <is>
-          <t>1-25-2008-09</t>
+          <t>2009-01-25</t>
         </is>
       </c>
     </row>
@@ -5575,55 +5642,55 @@
         </is>
       </c>
       <c r="D29" t="n">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="E29" t="n">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="F29" t="n">
         <v>28</v>
       </c>
       <c r="G29" t="n">
-        <v>0.391</v>
+        <v>0.378</v>
       </c>
       <c r="H29" t="n">
         <v>48.3</v>
       </c>
       <c r="I29" t="n">
-        <v>36.2</v>
+        <v>36</v>
       </c>
       <c r="J29" t="n">
         <v>78.5</v>
       </c>
       <c r="K29" t="n">
-        <v>0.461</v>
+        <v>0.459</v>
       </c>
       <c r="L29" t="n">
         <v>6.2</v>
       </c>
       <c r="M29" t="n">
-        <v>16.3</v>
+        <v>16.5</v>
       </c>
       <c r="N29" t="n">
-        <v>0.38</v>
+        <v>0.377</v>
       </c>
       <c r="O29" t="n">
-        <v>19.2</v>
+        <v>19.1</v>
       </c>
       <c r="P29" t="n">
-        <v>23.3</v>
+        <v>23.2</v>
       </c>
       <c r="Q29" t="n">
-        <v>0.824</v>
+        <v>0.823</v>
       </c>
       <c r="R29" t="n">
         <v>9</v>
       </c>
       <c r="S29" t="n">
-        <v>30</v>
+        <v>29.9</v>
       </c>
       <c r="T29" t="n">
-        <v>39</v>
+        <v>38.9</v>
       </c>
       <c r="U29" t="n">
         <v>21.8</v>
@@ -5641,55 +5708,55 @@
         <v>4.5</v>
       </c>
       <c r="Z29" t="n">
-        <v>19.5</v>
+        <v>19.6</v>
       </c>
       <c r="AA29" t="n">
         <v>20.9</v>
       </c>
       <c r="AB29" t="n">
-        <v>97.7</v>
+        <v>97.40000000000001</v>
       </c>
       <c r="AC29" t="n">
-        <v>-1.9</v>
+        <v>-2.3</v>
       </c>
       <c r="AD29" t="n">
-        <v>1</v>
+        <v>2</v>
       </c>
       <c r="AE29" t="n">
-        <v>19</v>
+        <v>22</v>
       </c>
       <c r="AF29" t="n">
         <v>24</v>
       </c>
       <c r="AG29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AH29" t="n">
         <v>18</v>
       </c>
       <c r="AI29" t="n">
+        <v>21</v>
+      </c>
+      <c r="AJ29" t="n">
+        <v>22</v>
+      </c>
+      <c r="AK29" t="n">
+        <v>10</v>
+      </c>
+      <c r="AL29" t="n">
+        <v>18</v>
+      </c>
+      <c r="AM29" t="n">
         <v>20</v>
       </c>
-      <c r="AJ29" t="n">
-        <v>23</v>
-      </c>
-      <c r="AK29" t="n">
+      <c r="AN29" t="n">
         <v>8</v>
-      </c>
-      <c r="AL29" t="n">
-        <v>19</v>
-      </c>
-      <c r="AM29" t="n">
-        <v>22</v>
-      </c>
-      <c r="AN29" t="n">
-        <v>6</v>
       </c>
       <c r="AO29" t="n">
         <v>14</v>
       </c>
       <c r="AP29" t="n">
-        <v>21</v>
+        <v>22</v>
       </c>
       <c r="AQ29" t="n">
         <v>1</v>
@@ -5698,7 +5765,7 @@
         <v>29</v>
       </c>
       <c r="AS29" t="n">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="AT29" t="n">
         <v>28</v>
@@ -5710,10 +5777,10 @@
         <v>9</v>
       </c>
       <c r="AW29" t="n">
-        <v>26</v>
+        <v>27</v>
       </c>
       <c r="AX29" t="n">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="AY29" t="n">
         <v>12</v>
@@ -5722,13 +5789,13 @@
         <v>4</v>
       </c>
       <c r="BA29" t="n">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="BB29" t="n">
         <v>20</v>
       </c>
       <c r="BC29" t="n">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="BD29" t="n">
         <v>10</v>
@@ -5740,7 +5807,7 @@
       </c>
       <c r="BF29" t="inlineStr">
         <is>
-          <t>1-25-2008-09</t>
+          <t>2009-01-25</t>
         </is>
       </c>
     </row>
@@ -5757,94 +5824,94 @@
         </is>
       </c>
       <c r="D30" t="n">
-        <v>45</v>
+        <v>44</v>
       </c>
       <c r="E30" t="n">
         <v>25</v>
       </c>
       <c r="F30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="G30" t="n">
-        <v>0.556</v>
+        <v>0.5679999999999999</v>
       </c>
       <c r="H30" t="n">
-        <v>48.4</v>
+        <v>48.5</v>
       </c>
       <c r="I30" t="n">
-        <v>37.9</v>
+        <v>38</v>
       </c>
       <c r="J30" t="n">
-        <v>80.2</v>
+        <v>80.09999999999999</v>
       </c>
       <c r="K30" t="n">
-        <v>0.473</v>
+        <v>0.475</v>
       </c>
       <c r="L30" t="n">
-        <v>4.5</v>
+        <v>4.6</v>
       </c>
       <c r="M30" t="n">
         <v>13.5</v>
       </c>
       <c r="N30" t="n">
-        <v>0.337</v>
+        <v>0.339</v>
       </c>
       <c r="O30" t="n">
-        <v>21.3</v>
+        <v>21.2</v>
       </c>
       <c r="P30" t="n">
-        <v>27.8</v>
+        <v>27.5</v>
       </c>
       <c r="Q30" t="n">
-        <v>0.768</v>
+        <v>0.773</v>
       </c>
       <c r="R30" t="n">
-        <v>12.1</v>
+        <v>11.9</v>
       </c>
       <c r="S30" t="n">
         <v>29.3</v>
       </c>
       <c r="T30" t="n">
-        <v>41.4</v>
+        <v>41.2</v>
       </c>
       <c r="U30" t="n">
-        <v>24.8</v>
+        <v>24.9</v>
       </c>
       <c r="V30" t="n">
-        <v>15.1</v>
+        <v>15</v>
       </c>
       <c r="W30" t="n">
         <v>8.800000000000001</v>
       </c>
       <c r="X30" t="n">
-        <v>5</v>
+        <v>4.9</v>
       </c>
       <c r="Y30" t="n">
         <v>4.9</v>
       </c>
       <c r="Z30" t="n">
-        <v>22.5</v>
+        <v>22.4</v>
       </c>
       <c r="AA30" t="n">
-        <v>23.6</v>
+        <v>23.5</v>
       </c>
       <c r="AB30" t="n">
-        <v>101.7</v>
+        <v>101.8</v>
       </c>
       <c r="AC30" t="n">
-        <v>2.3</v>
+        <v>2.8</v>
       </c>
       <c r="AD30" t="n">
-        <v>3</v>
+        <v>4</v>
       </c>
       <c r="AE30" t="n">
         <v>11</v>
       </c>
       <c r="AF30" t="n">
-        <v>15</v>
+        <v>14</v>
       </c>
       <c r="AG30" t="n">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="AH30" t="n">
         <v>12</v>
@@ -5865,7 +5932,7 @@
         <v>28</v>
       </c>
       <c r="AN30" t="n">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="AO30" t="n">
         <v>3</v>
@@ -5874,13 +5941,13 @@
         <v>3</v>
       </c>
       <c r="AQ30" t="n">
-        <v>14</v>
+        <v>11</v>
       </c>
       <c r="AR30" t="n">
         <v>8</v>
       </c>
       <c r="AS30" t="n">
-        <v>24</v>
+        <v>22</v>
       </c>
       <c r="AT30" t="n">
         <v>16</v>
@@ -5889,13 +5956,13 @@
         <v>1</v>
       </c>
       <c r="AV30" t="n">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="AW30" t="n">
         <v>2</v>
       </c>
       <c r="AX30" t="n">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="AY30" t="n">
         <v>16</v>
@@ -5922,7 +5989,7 @@
       </c>
       <c r="BF30" t="inlineStr">
         <is>
-          <t>1-25-2008-09</t>
+          <t>2009-01-25</t>
         </is>
       </c>
     </row>
@@ -6017,7 +6084,7 @@
         <v>-6.9</v>
       </c>
       <c r="AD31" t="n">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="AE31" t="n">
         <v>29</v>
@@ -6029,7 +6096,7 @@
         <v>29</v>
       </c>
       <c r="AH31" t="n">
-        <v>25</v>
+        <v>26</v>
       </c>
       <c r="AI31" t="n">
         <v>16</v>
@@ -6047,7 +6114,7 @@
         <v>24</v>
       </c>
       <c r="AN31" t="n">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="AO31" t="n">
         <v>29</v>
@@ -6068,10 +6135,10 @@
         <v>25</v>
       </c>
       <c r="AU31" t="n">
-        <v>21</v>
+        <v>18</v>
       </c>
       <c r="AV31" t="n">
-        <v>11</v>
+        <v>12</v>
       </c>
       <c r="AW31" t="n">
         <v>10</v>
@@ -6104,7 +6171,7 @@
       </c>
       <c r="BF31" t="inlineStr">
         <is>
-          <t>1-25-2008-09</t>
+          <t>2009-01-25</t>
         </is>
       </c>
     </row>
